--- a/TableStructure/DBTableStructure.xlsx
+++ b/TableStructure/DBTableStructure.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhi\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02288F65-8F66-4ED8-8078-CB4B6809D3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="14355" windowHeight="4695"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>User Table</t>
   </si>
@@ -69,15 +75,6 @@
     <t>role_type</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
     <t>Permission Table</t>
   </si>
   <si>
@@ -87,40 +84,37 @@
     <t>role_id</t>
   </si>
   <si>
-    <t>admin_read</t>
-  </si>
-  <si>
-    <t>admin_create</t>
-  </si>
-  <si>
-    <t>member_read</t>
-  </si>
-  <si>
-    <t>member_create</t>
-  </si>
-  <si>
-    <t>member_update</t>
-  </si>
-  <si>
-    <t>user_read</t>
-  </si>
-  <si>
-    <t>user_delete</t>
-  </si>
-  <si>
-    <t>user_update</t>
-  </si>
-  <si>
     <t>USER_ROLE TABLE</t>
   </si>
   <si>
     <t>user_id</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>MEMBER</t>
+  </si>
+  <si>
+    <t>admin:read</t>
+  </si>
+  <si>
+    <t>admin:create</t>
+  </si>
+  <si>
+    <t>management:read</t>
+  </si>
+  <si>
+    <t>management:create</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -614,14 +608,11 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -674,14 +665,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -719,7 +713,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -791,7 +785,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -964,24 +958,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1008,34 +1002,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>76823</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>4.039699074074074E-2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
+      <c r="I3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1045,7 +1038,7 @@
       <c r="C4">
         <v>28753</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>4.039699074074074E-2</v>
       </c>
       <c r="E4" t="s">
@@ -1054,250 +1047,177 @@
       <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
       <c r="I4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>2</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>3</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>1</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="B26">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
         <v>2</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="5">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>4</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>5</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>6</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>7</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>8</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>9</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>1</v>
-      </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>1</v>
-      </c>
-      <c r="B32" s="6">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>2</v>
-      </c>
-      <c r="B33" s="6">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>2</v>
-      </c>
-      <c r="B34" s="6">
-        <v>3</v>
-      </c>
-      <c r="C34" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1"/>
-    <hyperlink ref="B4" r:id="rId2"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
